--- a/artfynd/A 7148-2021 artfynd.xlsx
+++ b/artfynd/A 7148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129834315</v>
       </c>
       <c r="B2" t="n">
-        <v>43243</v>
+        <v>43246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7148-2021 artfynd.xlsx
+++ b/artfynd/A 7148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129834315</v>
       </c>
       <c r="B2" t="n">
-        <v>43247</v>
+        <v>43332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7148-2021 artfynd.xlsx
+++ b/artfynd/A 7148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129834315</v>
       </c>
       <c r="B2" t="n">
-        <v>43332</v>
+        <v>43247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
